--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-performer-event-extension.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-performer-event-extension.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension permettant d'ajouter un performer à l'élément event d'une Composition.</t>
+    <t>Extension permettant d'ajouter l'exécutant de l'évènement documenté. Ajout d'un performer à l'élément event d'une Composition.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -254,9 +254,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>Exécutant de l’évènement documenté</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -854,7 +851,7 @@
         <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>22</v>
@@ -917,10 +914,10 @@
         <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>76</v>
@@ -928,10 +925,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -942,25 +939,25 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1011,13 +1008,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1026,15 +1023,15 @@
         <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1057,13 +1054,13 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1102,19 +1099,19 @@
         <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1126,7 +1123,7 @@
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1134,10 +1131,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1145,10 +1142,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
@@ -1160,16 +1157,16 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1219,13 +1216,13 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
@@ -1234,15 +1231,15 @@
         <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1253,7 +1250,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1265,13 +1262,13 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1310,43 +1307,43 @@
         <v>76</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AC6" s="2"/>
       <c r="AD6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>76</v>
@@ -1356,7 +1353,7 @@
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -1368,13 +1365,13 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1425,22 +1422,22 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
